--- a/Dataset Discovery.xlsx
+++ b/Dataset Discovery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\workspace\Data-collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B291808-61DB-4725-A922-38E51C681B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E2DEBF-6BBE-4835-8497-6E799B078131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D5EBFA63-9DEE-455B-A316-15A5A1EB96B9}"/>
   </bookViews>
